--- a/G.A.M.M.A/modpack_addons/gamma_ammo_weapon_table.xlsx
+++ b/G.A.M.M.A/modpack_addons/gamma_ammo_weapon_table.xlsx
@@ -2049,28 +2049,28 @@
       </c>
       <c r="E24" s="9">
         <f t="shared" si="1"/>
-        <v>0.47732142857142856</v>
+        <v>0.6046071428571429</v>
       </c>
       <c r="F24" s="9">
         <f t="shared" si="2"/>
-        <v>0.40178571428571425</v>
+        <v>0.37500000000000006</v>
       </c>
       <c r="G24" s="3">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H24" s="3">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="I24">
         <v>0.45</v>
       </c>
       <c r="J24">
         <f t="shared" si="12"/>
-        <v>0.27</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="K24" s="2">
         <f>J24*Feuil2!$B$1</f>
-        <v>17.82</v>
+        <v>22.572000000000003</v>
       </c>
       <c r="L24" s="1">
         <v>378</v>
@@ -2103,36 +2103,36 @@
         <v>55</v>
       </c>
       <c r="C25" s="3">
-        <v>960</v>
+        <v>1150</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" ref="D25:D29" si="14">C25/15</f>
-        <v>64</v>
+        <v>76.666666666666671</v>
       </c>
       <c r="E25" s="10">
         <f t="shared" si="1"/>
-        <v>0.51046875000000003</v>
+        <v>0.54234782608695642</v>
       </c>
       <c r="F25" s="9">
         <f t="shared" si="2"/>
-        <v>0.15625</v>
+        <v>0.10434782608695652</v>
       </c>
       <c r="G25" s="3">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H25" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="I25">
         <v>0.45</v>
       </c>
       <c r="J25">
         <f t="shared" ref="J25:J27" si="15">I25*H25</f>
-        <v>0.49500000000000005</v>
+        <v>0.63</v>
       </c>
       <c r="K25" s="2">
         <f>J25*Feuil2!$B$1</f>
-        <v>32.67</v>
+        <v>41.58</v>
       </c>
       <c r="L25" s="1">
         <v>378</v>
@@ -2173,28 +2173,28 @@
       </c>
       <c r="E26" s="9">
         <f t="shared" si="1"/>
-        <v>0.22275</v>
+        <v>0.28215000000000001</v>
       </c>
       <c r="F26" s="8">
         <f t="shared" si="2"/>
-        <v>0.375</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="G26" s="3">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H26" s="3">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="I26">
         <v>0.45</v>
       </c>
       <c r="J26">
         <f t="shared" si="15"/>
-        <v>0.27</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="K26" s="2">
         <f>J26*Feuil2!$B$1</f>
-        <v>17.82</v>
+        <v>22.572000000000003</v>
       </c>
       <c r="L26" s="1">
         <v>378</v>
@@ -2363,10 +2363,10 @@
       </c>
       <c r="F29" s="8">
         <f t="shared" si="2"/>
-        <v>0.24255319148936172</v>
+        <v>0.21702127659574472</v>
       </c>
       <c r="G29" s="3">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H29" s="3">
         <v>0.7</v>
